--- a/stacked_model/results/validation/model_b_controls_plus_measured_deposition_summary.xlsx
+++ b/stacked_model/results/validation/model_b_controls_plus_measured_deposition_summary.xlsx
@@ -553,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="F2" t="n">
         <v>50</v>
@@ -562,40 +562,40 @@
         <v>1900</v>
       </c>
       <c r="H2" t="n">
-        <v>3.447887237511382</v>
+        <v>3.375774780228361</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7875371416057402</v>
+        <v>0.7255111194052896</v>
       </c>
       <c r="J2" t="n">
-        <v>5.507973706548642</v>
+        <v>5.349084714321098</v>
       </c>
       <c r="K2" t="n">
-        <v>1.963807214309979</v>
+        <v>1.645171125477299</v>
       </c>
       <c r="L2" t="n">
-        <v>0.827016370056226</v>
+        <v>0.8384849534308451</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1284825610013011</v>
+        <v>0.1023818873599492</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8594736842105264</v>
+        <v>0.8289473684210528</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05540746337425231</v>
+        <v>0.05805806470481389</v>
       </c>
       <c r="P2" t="n">
-        <v>3.009890333438893</v>
+        <v>3.070287747041409</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4527914364730061</v>
+        <v>0.4963363258348464</v>
       </c>
       <c r="R2" t="n">
-        <v>-54.6169184348223</v>
+        <v>-54.83226482951265</v>
       </c>
       <c r="S2" t="n">
-        <v>7.913167714040959</v>
+        <v>7.70887402540654</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1e-10</v>
+        <v>1e-06</v>
       </c>
       <c r="F3" t="n">
         <v>50</v>
@@ -627,40 +627,40 @@
         <v>1900</v>
       </c>
       <c r="H3" t="n">
-        <v>3.447887275595192</v>
+        <v>3.372599242991528</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7875371510231362</v>
+        <v>0.7213625728310327</v>
       </c>
       <c r="J3" t="n">
-        <v>5.50797380782198</v>
+        <v>5.356006034364061</v>
       </c>
       <c r="K3" t="n">
-        <v>1.963807319298807</v>
+        <v>1.645455832483003</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8270163620847605</v>
+        <v>0.8382019882517224</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1284825693527775</v>
+        <v>0.1022799364734058</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8594736842105264</v>
+        <v>0.8605263157894736</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05540746337425231</v>
+        <v>0.05402296189172899</v>
       </c>
       <c r="P3" t="n">
-        <v>3.009885056327977</v>
+        <v>2.994317943345729</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4527857461033208</v>
+        <v>0.4173663509299333</v>
       </c>
       <c r="R3" t="n">
-        <v>-54.61691843486106</v>
+        <v>-54.86709171451206</v>
       </c>
       <c r="S3" t="n">
-        <v>7.913167714059463</v>
+        <v>7.75310694557309</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01</v>
+        <v>1e-10</v>
       </c>
       <c r="F4" t="n">
         <v>50</v>
@@ -692,40 +692,40 @@
         <v>1900</v>
       </c>
       <c r="H4" t="n">
-        <v>3.459275160214174</v>
+        <v>3.372599257012384</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8121892375948289</v>
+        <v>0.7213626256790601</v>
       </c>
       <c r="J4" t="n">
-        <v>5.509337043310608</v>
+        <v>5.356006045889773</v>
       </c>
       <c r="K4" t="n">
-        <v>1.952084939048284</v>
+        <v>1.645455687921243</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8272428581145455</v>
+        <v>0.8382019910561094</v>
       </c>
       <c r="M4" t="n">
-        <v>0.125246033848036</v>
+        <v>0.1022799091693006</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8273684210526316</v>
+        <v>0.8605263157894736</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06811880693477368</v>
+        <v>0.05402296189172899</v>
       </c>
       <c r="P4" t="n">
-        <v>3.097379074359492</v>
+        <v>2.994312942399523</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.523679556470001</v>
+        <v>0.4173601342127395</v>
       </c>
       <c r="R4" t="n">
-        <v>-54.52704701592004</v>
+        <v>-54.86709171470655</v>
       </c>
       <c r="S4" t="n">
-        <v>7.920303107969939</v>
+        <v>7.753106945679795</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -741,14 +741,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rbf</t>
+          <t>matern_1.5</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="F5" t="n">
         <v>50</v>
@@ -757,40 +757,40 @@
         <v>1900</v>
       </c>
       <c r="H5" t="n">
-        <v>3.468473355900116</v>
+        <v>3.357886682371592</v>
       </c>
       <c r="I5" t="n">
-        <v>0.803553863307471</v>
+        <v>0.7131247252207706</v>
       </c>
       <c r="J5" t="n">
-        <v>5.528016143051469</v>
+        <v>5.420072556009692</v>
       </c>
       <c r="K5" t="n">
-        <v>1.936064294617601</v>
+        <v>1.639885913294939</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8264153479628094</v>
+        <v>0.8343743216583303</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1246657795469599</v>
+        <v>0.1048558694566506</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8557894736842105</v>
+        <v>0.8263157894736842</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05878141439305884</v>
+        <v>0.06061847931051541</v>
       </c>
       <c r="P5" t="n">
-        <v>3.009765652514613</v>
+        <v>3.082196412834537</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4442078974580527</v>
+        <v>0.4955254578678781</v>
       </c>
       <c r="R5" t="n">
-        <v>-54.51119522962355</v>
+        <v>-53.81904058446682</v>
       </c>
       <c r="S5" t="n">
-        <v>7.912920955870979</v>
+        <v>7.870216284299254</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -806,14 +806,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rbf</t>
+          <t>matern_1.5</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01</v>
+        <v>1e-10</v>
       </c>
       <c r="F6" t="n">
         <v>50</v>
@@ -822,40 +822,40 @@
         <v>1900</v>
       </c>
       <c r="H6" t="n">
-        <v>3.468660819270315</v>
+        <v>3.362952490272983</v>
       </c>
       <c r="I6" t="n">
-        <v>0.790914866690111</v>
+        <v>0.7090264169388196</v>
       </c>
       <c r="J6" t="n">
-        <v>5.538786162479036</v>
+        <v>5.428073178793333</v>
       </c>
       <c r="K6" t="n">
-        <v>1.959574955423372</v>
+        <v>1.630924020065625</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8252038112562962</v>
+        <v>0.8340583718911307</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1282380298588301</v>
+        <v>0.1045508489490338</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8336842105263158</v>
+        <v>0.8547368421052631</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06499303093225356</v>
+        <v>0.05781167755410851</v>
       </c>
       <c r="P6" t="n">
-        <v>3.098044252837302</v>
+        <v>2.99353673944706</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.52910237251472</v>
+        <v>0.4159480555905435</v>
       </c>
       <c r="R6" t="n">
-        <v>-54.75091726418832</v>
+        <v>-53.75051636982636</v>
       </c>
       <c r="S6" t="n">
-        <v>8.105095009580612</v>
+        <v>7.878296062357085</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -871,14 +871,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rbf</t>
+          <t>matern_1.5</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1e-10</v>
+        <v>1e-06</v>
       </c>
       <c r="F7" t="n">
         <v>50</v>
@@ -887,40 +887,40 @@
         <v>1900</v>
       </c>
       <c r="H7" t="n">
-        <v>3.499069919705792</v>
+        <v>3.362953687708487</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7440163202987629</v>
+        <v>0.7090275254235656</v>
       </c>
       <c r="J7" t="n">
-        <v>5.59619661048285</v>
+        <v>5.428076643239733</v>
       </c>
       <c r="K7" t="n">
-        <v>1.842224595039959</v>
+        <v>1.63092486503835</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8234702003406418</v>
+        <v>0.8340581772537368</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1208181385010656</v>
+        <v>0.1045509049095321</v>
       </c>
       <c r="N7" t="n">
-        <v>0.853157894736842</v>
+        <v>0.8547368421052631</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05993617876931932</v>
+        <v>0.05781167755410851</v>
       </c>
       <c r="P7" t="n">
-        <v>3.023469767367615</v>
+        <v>2.993543248589899</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4385692286954482</v>
+        <v>0.4159544236593705</v>
       </c>
       <c r="R7" t="n">
-        <v>-54.47254933674228</v>
+        <v>-53.75051636901658</v>
       </c>
       <c r="S7" t="n">
-        <v>7.872651852995056</v>
+        <v>7.878296062686805</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -936,14 +936,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>matern_1.5</t>
+          <t>rbf</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01</v>
+        <v>1e-10</v>
       </c>
       <c r="F8" t="n">
         <v>50</v>
@@ -952,40 +952,40 @@
         <v>1900</v>
       </c>
       <c r="H8" t="n">
-        <v>3.429613100914366</v>
+        <v>3.44483605482529</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7591323062822439</v>
+        <v>0.7209664341614913</v>
       </c>
       <c r="J8" t="n">
-        <v>5.643689651156511</v>
+        <v>5.446421742711656</v>
       </c>
       <c r="K8" t="n">
-        <v>1.87683509332247</v>
+        <v>1.602730747218287</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8196308997603325</v>
+        <v>0.8334970285676591</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1251619386446413</v>
+        <v>0.1023317121213992</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8278947368421053</v>
+        <v>0.8510526315789474</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06450628299710111</v>
+        <v>0.05838819098802408</v>
       </c>
       <c r="P8" t="n">
-        <v>3.081228253668448</v>
+        <v>3.013276536006227</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4565140905803406</v>
+        <v>0.4289708577284528</v>
       </c>
       <c r="R8" t="n">
-        <v>-53.73927493822739</v>
+        <v>-54.60918874275697</v>
       </c>
       <c r="S8" t="n">
-        <v>7.787635462848805</v>
+        <v>7.667598933928912</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1001,14 +1001,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>matern_1.5</t>
+          <t>rbf</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01</v>
+        <v>1e-06</v>
       </c>
       <c r="F9" t="n">
         <v>50</v>
@@ -1017,40 +1017,40 @@
         <v>1900</v>
       </c>
       <c r="H9" t="n">
-        <v>3.440446096052899</v>
+        <v>3.45855682257341</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7648585014647746</v>
+        <v>0.709346437644061</v>
       </c>
       <c r="J9" t="n">
-        <v>5.64655203064743</v>
+        <v>5.465151823334768</v>
       </c>
       <c r="K9" t="n">
-        <v>1.88594714573904</v>
+        <v>1.586697487549569</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8192593325733032</v>
+        <v>0.8326165242210425</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1257029561095357</v>
+        <v>0.1018263341594471</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8289473684210528</v>
+        <v>0.8505263157894737</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06538544034182737</v>
+        <v>0.05858875109406964</v>
       </c>
       <c r="P9" t="n">
-        <v>3.084886576573993</v>
+        <v>3.016109475361398</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4768533605801636</v>
+        <v>0.4274900597569351</v>
       </c>
       <c r="R9" t="n">
-        <v>-53.66939707665025</v>
+        <v>-54.57895605954977</v>
       </c>
       <c r="S9" t="n">
-        <v>7.845857053903265</v>
+        <v>7.653667896448739</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -1066,14 +1066,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>matern_1.5</t>
+          <t>rbf</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>1e-10</v>
+        <v>0.01</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
@@ -1082,40 +1082,40 @@
         <v>1900</v>
       </c>
       <c r="H10" t="n">
-        <v>3.436332446224732</v>
+        <v>3.448817432492355</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7563266418987965</v>
+        <v>0.6730291939744064</v>
       </c>
       <c r="J10" t="n">
-        <v>5.659836543776469</v>
+        <v>5.471951794460174</v>
       </c>
       <c r="K10" t="n">
-        <v>1.868858499606933</v>
+        <v>1.544686559015644</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8187714039771197</v>
+        <v>0.8329449590765416</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1248289752560844</v>
+        <v>0.09917339540998758</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8542105263157893</v>
+        <v>0.8189473684210529</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05877420091694392</v>
+        <v>0.06460042563612206</v>
       </c>
       <c r="P10" t="n">
-        <v>3.006091634867496</v>
+        <v>3.10403123753315</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4016435718181773</v>
+        <v>0.4896261721429646</v>
       </c>
       <c r="R10" t="n">
-        <v>-53.63197167737106</v>
+        <v>-54.64522391765543</v>
       </c>
       <c r="S10" t="n">
-        <v>7.843213088450745</v>
+        <v>7.642219094877765</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>1e-06</v>
@@ -1147,40 +1147,40 @@
         <v>1900</v>
       </c>
       <c r="H11" t="n">
-        <v>3.436332599900075</v>
+        <v>3.396178073364758</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7563268730264879</v>
+        <v>0.7169407873639657</v>
       </c>
       <c r="J11" t="n">
-        <v>5.659837462107099</v>
+        <v>5.477859126268156</v>
       </c>
       <c r="K11" t="n">
-        <v>1.868859419004503</v>
+        <v>1.631822415420769</v>
       </c>
       <c r="L11" t="n">
-        <v>0.818771342878918</v>
+        <v>0.8311169301944471</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1248290448309067</v>
+        <v>0.1046640948659288</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8542105263157893</v>
+        <v>0.8531578947368422</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05877420091694392</v>
+        <v>0.05969991098285434</v>
       </c>
       <c r="P11" t="n">
-        <v>3.006098255329228</v>
+        <v>3.007387942759916</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4016483677495769</v>
+        <v>0.4169916726660465</v>
       </c>
       <c r="R11" t="n">
-        <v>-53.63197167465214</v>
+        <v>-53.58137344077632</v>
       </c>
       <c r="S11" t="n">
-        <v>7.843213087692713</v>
+        <v>7.906737794648699</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1203,7 +1203,7 @@
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>1e-06</v>
+        <v>1e-10</v>
       </c>
       <c r="F12" t="n">
         <v>50</v>
@@ -1212,40 +1212,40 @@
         <v>1900</v>
       </c>
       <c r="H12" t="n">
-        <v>3.457794578556639</v>
+        <v>3.390550478344702</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7569918640948623</v>
+        <v>0.7212641940945085</v>
       </c>
       <c r="J12" t="n">
-        <v>5.682866503474174</v>
+        <v>5.479337827550622</v>
       </c>
       <c r="K12" t="n">
-        <v>1.860206063003446</v>
+        <v>1.623387913362152</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8175384608051202</v>
+        <v>0.8310580946669941</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1247506786415152</v>
+        <v>0.1042535344231667</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8521052631578947</v>
+        <v>0.8526315789473685</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05917680147089036</v>
+        <v>0.05944130940166126</v>
       </c>
       <c r="P12" t="n">
-        <v>3.010248538532638</v>
+        <v>3.005250228188988</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4147124835740001</v>
+        <v>0.4186318922284278</v>
       </c>
       <c r="R12" t="n">
-        <v>-53.54928182938434</v>
+        <v>-53.67014624688863</v>
       </c>
       <c r="S12" t="n">
-        <v>7.915167841919645</v>
+        <v>7.923729991811849</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1268,7 +1268,7 @@
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>1e-10</v>
+        <v>0.01</v>
       </c>
       <c r="F13" t="n">
         <v>50</v>
@@ -1277,40 +1277,40 @@
         <v>1900</v>
       </c>
       <c r="H13" t="n">
-        <v>3.462833937236998</v>
+        <v>3.39285476723357</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7525976023288448</v>
+        <v>0.7217798517832983</v>
       </c>
       <c r="J13" t="n">
-        <v>5.683712899246404</v>
+        <v>5.47982023424492</v>
       </c>
       <c r="K13" t="n">
-        <v>1.859530455790427</v>
+        <v>1.636193870822864</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8174976504668363</v>
+        <v>0.8312882954259142</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1247238303781713</v>
+        <v>0.1040981070045149</v>
       </c>
       <c r="N13" t="n">
-        <v>0.851578947368421</v>
+        <v>0.8226315789473684</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05890630762646884</v>
+        <v>0.06057416499332897</v>
       </c>
       <c r="P13" t="n">
-        <v>3.00884706545734</v>
+        <v>3.094319834721072</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4158906617536172</v>
+        <v>0.4892588024978038</v>
       </c>
       <c r="R13" t="n">
-        <v>-53.53953091286057</v>
+        <v>-53.63823416537296</v>
       </c>
       <c r="S13" t="n">
-        <v>7.909509779012843</v>
+        <v>7.764241896043386</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
